--- a/_ProjectKaskan__Unpublished/Rachael_Robinson_dissertation_file_copies/Brains data for animals/blind mole rat .xlsx
+++ b/_ProjectKaskan__Unpublished/Rachael_Robinson_dissertation_file_copies/Brains data for animals/blind mole rat .xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23801"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachael\OneDrive\Documents\PS30094 Dissertation\Brain area data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/_ProjectKaskan__Unpublished/Rachael_Robinson_dissertation_file_copies/Brains data for animals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B519AD28-ED4C-4DF1-884C-9B98AD02CAA8}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{B519AD28-ED4C-4DF1-884C-9B98AD02CAA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B7D9688-A6CD-3349-8BC3-87A5534221BA}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{6D1477F4-83B1-47A4-9A26-3C2A3DBD56EF}"/>
+    <workbookView xWindow="72340" yWindow="-3560" windowWidth="25560" windowHeight="15900" xr2:uid="{6D1477F4-83B1-47A4-9A26-3C2A3DBD56EF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -247,7 +247,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -394,9 +394,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -434,7 +434,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -540,7 +540,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -682,7 +682,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -691,9 +691,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CED8AE1-83F9-4EB3-ADEC-DA505152B3D9}">
   <dimension ref="A1:S22"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:19" ht="18.5">
+    <row r="1" spans="1:19" ht="19" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -737,7 +737,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="15.5">
+    <row r="2" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -788,7 +788,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="18.5">
+    <row r="3" spans="1:19" ht="19" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -840,7 +840,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="18.5">
+    <row r="4" spans="1:19" ht="19" x14ac:dyDescent="0.2">
       <c r="H4" s="5" t="s">
         <v>25</v>
       </c>
@@ -864,7 +864,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="18.5">
+    <row r="5" spans="1:19" ht="19" x14ac:dyDescent="0.2">
       <c r="H5" s="5"/>
       <c r="I5" s="9" t="s">
         <v>29</v>
@@ -880,7 +880,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="18.5">
+    <row r="6" spans="1:19" ht="19" x14ac:dyDescent="0.2">
       <c r="H6" s="5"/>
       <c r="I6" s="9" t="s">
         <v>30</v>
@@ -896,7 +896,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="18.5">
+    <row r="7" spans="1:19" ht="19" x14ac:dyDescent="0.2">
       <c r="H7" s="5"/>
       <c r="I7" s="9" t="s">
         <v>32</v>
@@ -912,7 +912,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="18.5">
+    <row r="8" spans="1:19" ht="19" x14ac:dyDescent="0.2">
       <c r="H8" s="5"/>
       <c r="I8" s="9" t="s">
         <v>33</v>
@@ -928,7 +928,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="18.5">
+    <row r="9" spans="1:19" ht="19" x14ac:dyDescent="0.2">
       <c r="H9" s="5"/>
       <c r="I9" s="9" t="s">
         <v>34</v>
@@ -947,7 +947,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="18.5">
+    <row r="10" spans="1:19" ht="19" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>3</v>
       </c>
@@ -984,7 +984,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="18.5">
+    <row r="11" spans="1:19" ht="19" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>4</v>
       </c>
@@ -1021,7 +1021,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="18.5">
+    <row r="12" spans="1:19" ht="19" x14ac:dyDescent="0.2">
       <c r="H12" s="5"/>
       <c r="I12" s="9" t="s">
         <v>37</v>
@@ -1037,7 +1037,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="18.5">
+    <row r="13" spans="1:19" ht="19" x14ac:dyDescent="0.2">
       <c r="H13" s="5"/>
       <c r="I13" s="9" t="s">
         <v>38</v>
@@ -1053,7 +1053,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="18.5">
+    <row r="14" spans="1:19" ht="19" x14ac:dyDescent="0.2">
       <c r="H14" s="5"/>
       <c r="I14" s="9">
         <v>1</v>
@@ -1069,7 +1069,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="18.5">
+    <row r="15" spans="1:19" ht="19" x14ac:dyDescent="0.2">
       <c r="H15" s="5"/>
       <c r="I15" s="9">
         <v>2</v>
@@ -1085,7 +1085,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="18.5">
+    <row r="16" spans="1:19" ht="19" x14ac:dyDescent="0.2">
       <c r="H16" s="5"/>
       <c r="I16" s="9" t="s">
         <v>39</v>
@@ -1101,7 +1101,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="8:13" ht="18.5">
+    <row r="17" spans="8:13" ht="19" x14ac:dyDescent="0.2">
       <c r="H17" s="5"/>
       <c r="I17" s="9" t="s">
         <v>40</v>
@@ -1117,7 +1117,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="8:13" ht="18.5">
+    <row r="18" spans="8:13" ht="19" x14ac:dyDescent="0.2">
       <c r="H18" s="5"/>
       <c r="I18" s="9" t="s">
         <v>41</v>
@@ -1133,7 +1133,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="8:13" ht="18.5">
+    <row r="19" spans="8:13" ht="19" x14ac:dyDescent="0.2">
       <c r="H19" s="5"/>
       <c r="I19" s="9" t="s">
         <v>42</v>
@@ -1149,7 +1149,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="8:13" ht="18.5">
+    <row r="20" spans="8:13" ht="19" x14ac:dyDescent="0.2">
       <c r="H20" s="5"/>
       <c r="I20" s="9" t="s">
         <v>43</v>
@@ -1165,7 +1165,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="8:13" ht="18.5">
+    <row r="21" spans="8:13" ht="19" x14ac:dyDescent="0.2">
       <c r="H21" s="5"/>
       <c r="I21" s="9" t="s">
         <v>44</v>
@@ -1181,7 +1181,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="8:13" ht="15.5">
+    <row r="22" spans="8:13" ht="16" x14ac:dyDescent="0.2">
       <c r="I22" s="9" t="s">
         <v>45</v>
       </c>
@@ -1202,6 +1202,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="66af2654134d243f62aac8e2b322f1d6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2bc3adf68671d86faa9c37249f400344" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
@@ -1444,19 +1453,29 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DA15090-D56A-462C-9BC4-E3184A2BEF7D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB6C1A30-1D8A-4606-B9CE-8898D830D253}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB6C1A30-1D8A-4606-B9CE-8898D830D253}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DA15090-D56A-462C-9BC4-E3184A2BEF7D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>